--- a/academias/Inglés - Estadisticos 20232.xlsx
+++ b/academias/Inglés - Estadisticos 20232.xlsx
@@ -1574,25 +1574,25 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1609,25 +1609,25 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>11.9</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1644,25 +1644,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1679,25 +1679,25 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1714,25 +1714,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1749,25 +1749,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1781,25 +1781,25 @@
         <v>220</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="F8">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1851,25 +1851,25 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>34.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1921,25 +1921,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1956,25 +1956,25 @@
         <v>25</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1991,25 +1991,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2023,25 +2023,25 @@
         <v>151</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F15">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>17.2</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2265,25 +2265,25 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2300,25 +2300,25 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>79.3</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J23">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2335,25 +2335,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2370,25 +2370,25 @@
         <v>12</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2402,25 +2402,25 @@
         <v>104</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F26">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2437,25 +2437,25 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J27">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2469,25 +2469,25 @@
         <v>31</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F28">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J28">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2498,25 +2498,25 @@
         <v>667</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="F29">
-        <v>667</v>
+        <v>280</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
-        <v>667</v>
+        <v>161</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>24.1</v>
       </c>
     </row>
   </sheetData>
@@ -2584,19 +2584,19 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H2" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>5.7</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>91.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="H5" s="1">
-        <v>8.9</v>
+        <v>22.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2724,19 +2724,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2759,19 +2759,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>94.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2791,16 +2791,16 @@
         <v>220</v>
       </c>
       <c r="E8">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1">
-        <v>90</v>
+        <v>86.8</v>
       </c>
       <c r="H8" s="1">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="2">
         <v>8</v>
@@ -2826,19 +2826,19 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>65.2</v>
+        <v>91.3</v>
       </c>
       <c r="H9" s="1">
-        <v>34.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2861,19 +2861,19 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>47.8</v>
+        <v>65.2</v>
       </c>
       <c r="H10" s="1">
-        <v>52.2</v>
+        <v>34.8</v>
       </c>
       <c r="I10" s="2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2896,19 +2896,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>80.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="H11" s="1">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>21.1</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2966,19 +2966,19 @@
         <v>25</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I14" s="2">
         <v>8.1</v>
@@ -3033,19 +3033,19 @@
         <v>151</v>
       </c>
       <c r="E15">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
-        <v>78.8</v>
+        <v>82.8</v>
       </c>
       <c r="H15" s="1">
-        <v>21.2</v>
+        <v>17.2</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3275,19 +3275,19 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
-        <v>26.7</v>
+        <v>36.7</v>
       </c>
       <c r="H22" s="1">
-        <v>73.3</v>
+        <v>63.3</v>
       </c>
       <c r="I22" s="2">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3310,16 +3310,16 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="H23" s="1">
-        <v>75.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I23" s="2">
         <v>5.3</v>
@@ -3345,19 +3345,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G24" s="1">
-        <v>42.4</v>
+        <v>54.5</v>
       </c>
       <c r="H24" s="1">
-        <v>57.6</v>
+        <v>45.5</v>
       </c>
       <c r="I24" s="2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>58.3</v>
       </c>
       <c r="I25" s="2">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3412,19 +3412,19 @@
         <v>104</v>
       </c>
       <c r="E26">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F26">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1">
-        <v>32.7</v>
+        <v>38.5</v>
       </c>
       <c r="H26" s="1">
-        <v>67.3</v>
+        <v>61.5</v>
       </c>
       <c r="I26" s="2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3447,19 +3447,19 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3479,19 +3479,19 @@
         <v>31</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>667</v>
       </c>
       <c r="E29">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F29">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G29" s="1">
-        <v>77.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="I29" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20232.xlsx
+++ b/academias/Inglés - Estadisticos 20232.xlsx
@@ -2058,25 +2058,25 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2093,25 +2093,25 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>89.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>10.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2128,25 +2128,25 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2163,25 +2163,25 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2198,25 +2198,25 @@
         <v>38</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2230,25 +2230,25 @@
         <v>161</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2498,25 +2498,25 @@
         <v>667</v>
       </c>
       <c r="E29">
-        <v>387</v>
+        <v>527</v>
       </c>
       <c r="F29">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="G29" s="1">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H29" s="1">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>24.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3068,19 +3068,19 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H16" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I16" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3103,19 +3103,19 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>92.3</v>
+        <v>89.7</v>
       </c>
       <c r="H17" s="1">
-        <v>7.7</v>
+        <v>10.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3138,19 +3138,19 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>8.6</v>
+        <v>11.4</v>
       </c>
       <c r="I18" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3173,19 +3173,19 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H19" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3208,19 +3208,19 @@
         <v>38</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>81.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H20" s="1">
-        <v>18.4</v>
+        <v>5.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3240,19 +3240,19 @@
         <v>161</v>
       </c>
       <c r="E21">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1">
-        <v>85.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="H21" s="1">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3508,16 +3508,16 @@
         <v>667</v>
       </c>
       <c r="E29">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F29">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G29" s="1">
-        <v>78.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="H29" s="1">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2">
         <v>7.4</v>

--- a/academias/Inglés - Estadisticos 20232.xlsx
+++ b/academias/Inglés - Estadisticos 20232.xlsx
@@ -1586,7 +1586,7 @@
         <v>13.8</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2584,19 +2584,19 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>88.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>11.9</v>
+        <v>7.1</v>
       </c>
       <c r="I3" s="2">
         <v>8</v>
@@ -2654,16 +2654,16 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I4" s="2">
         <v>8.300000000000001</v>
@@ -2689,19 +2689,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="H5" s="1">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2724,19 +2724,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2759,19 +2759,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H7" s="1">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2791,19 +2791,19 @@
         <v>220</v>
       </c>
       <c r="E8">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>86.8</v>
+        <v>94.5</v>
       </c>
       <c r="H8" s="1">
-        <v>13.2</v>
+        <v>5.5</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2826,19 +2826,19 @@
         <v>23</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>91.3</v>
+        <v>78.3</v>
       </c>
       <c r="H9" s="1">
-        <v>8.699999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="I9" s="2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2861,19 +2861,19 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>65.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>34.8</v>
+        <v>26.1</v>
       </c>
       <c r="I10" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2896,19 +2896,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="H11" s="1">
-        <v>29</v>
+        <v>35.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>21.1</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>4</v>
       </c>
       <c r="I13" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3001,19 +3001,19 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="H14" s="1">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>151</v>
       </c>
       <c r="E15">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1">
-        <v>82.8</v>
+        <v>79.5</v>
       </c>
       <c r="H15" s="1">
-        <v>17.2</v>
+        <v>20.5</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3068,16 +3068,16 @@
         <v>25</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H16" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I16" s="2">
         <v>6.9</v>
@@ -3103,19 +3103,19 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>89.7</v>
+        <v>92.3</v>
       </c>
       <c r="H17" s="1">
-        <v>10.3</v>
+        <v>7.7</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>11.4</v>
       </c>
       <c r="I18" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3173,19 +3173,19 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H19" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3240,16 +3240,16 @@
         <v>161</v>
       </c>
       <c r="E21">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="H21" s="1">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I21" s="2">
         <v>7.7</v>
@@ -3275,19 +3275,19 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G22" s="1">
-        <v>36.7</v>
+        <v>76.7</v>
       </c>
       <c r="H22" s="1">
-        <v>63.3</v>
+        <v>23.3</v>
       </c>
       <c r="I22" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3310,19 +3310,19 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>20.7</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3345,19 +3345,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>54.5</v>
+        <v>78.8</v>
       </c>
       <c r="H24" s="1">
-        <v>45.5</v>
+        <v>21.2</v>
       </c>
       <c r="I24" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3380,19 +3380,19 @@
         <v>12</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>41.7</v>
+        <v>75</v>
       </c>
       <c r="H25" s="1">
-        <v>58.3</v>
+        <v>25</v>
       </c>
       <c r="I25" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3412,19 +3412,19 @@
         <v>104</v>
       </c>
       <c r="E26">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="F26">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1">
-        <v>38.5</v>
+        <v>83.7</v>
       </c>
       <c r="H26" s="1">
-        <v>61.5</v>
+        <v>16.3</v>
       </c>
       <c r="I26" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>667</v>
       </c>
       <c r="E29">
-        <v>527</v>
+        <v>593</v>
       </c>
       <c r="F29">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="G29" s="1">
-        <v>79</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H29" s="1">
-        <v>21</v>
+        <v>11.1</v>
       </c>
       <c r="I29" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
         <v>0</v>
